--- a/forecasting/DboFizObTic.xlsx
+++ b/forecasting/DboFizObTic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\OneDrive\Рабочий стол\НИР\Итог\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\PycharmProjects\NIR2\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E05C25-DB4F-46AC-9D5E-AD4DC004FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6888972-AB04-4B80-8D54-103783ED10BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16680" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>I квартал 2021</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>III квартал  2025</t>
+  </si>
+  <si>
+    <t>IV квартал 2025</t>
+  </si>
+  <si>
+    <t>I квартал  2026</t>
   </si>
 </sst>
 </file>
@@ -198,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -210,9 +216,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -242,6 +245,10 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -524,19 +531,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10">
+      <c r="B1" s="9">
         <v>1126831.54</v>
       </c>
       <c r="C1" s="1"/>
@@ -545,7 +552,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>1239244.71</v>
       </c>
       <c r="C2" s="1"/>
@@ -554,7 +561,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>1687955.5</v>
       </c>
       <c r="C3" s="1"/>
@@ -563,7 +570,7 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>1965668.25</v>
       </c>
       <c r="C4" s="1"/>
@@ -572,7 +579,7 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>1660927.42</v>
       </c>
       <c r="C5" s="1"/>
@@ -581,7 +588,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>1807456.44</v>
       </c>
       <c r="C6" s="1"/>
@@ -590,7 +597,7 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>2722794.85</v>
       </c>
       <c r="C7" s="1"/>
@@ -599,7 +606,7 @@
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>3046331.29</v>
       </c>
       <c r="C8" s="1"/>
@@ -608,7 +615,7 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>2489788.9</v>
       </c>
       <c r="C9" s="1"/>
@@ -617,7 +624,7 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>1027385.45</v>
       </c>
       <c r="C10" s="1"/>
@@ -626,7 +633,7 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>547223.71</v>
       </c>
       <c r="C11" s="1"/>
@@ -635,7 +642,7 @@
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>586671.94000000018</v>
       </c>
       <c r="C12" s="1"/>
@@ -644,7 +651,7 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>901694.62</v>
       </c>
       <c r="C13" s="1"/>
@@ -653,7 +660,7 @@
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <v>970073.68</v>
       </c>
       <c r="C14" s="1"/>
@@ -662,7 +669,7 @@
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>3819517.48</v>
       </c>
       <c r="C15" s="1"/>
@@ -671,56 +678,65 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>3911284.2200000011</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>2903273.23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>2224599.81</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>2704559.76</v>
       </c>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="8"/>
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
+        <v>20420827.200000003</v>
+      </c>
       <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="8"/>
+      <c r="D20" s="15"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="16">
+        <v>6824564</v>
+      </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="1"/>
     </row>
   </sheetData>

--- a/forecasting/DboFizObTic.xlsx
+++ b/forecasting/DboFizObTic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\PycharmProjects\NIR2\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6888972-AB04-4B80-8D54-103783ED10BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D8D81E-A501-468B-8134-6FDB17BFD529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -246,8 +246,10 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -714,18 +716,18 @@
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="7">
-        <v>20420827.200000003</v>
+      <c r="B20" s="8">
+        <v>2795977.1999999993</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="15"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="16">
-        <v>6824564</v>
+      <c r="B21" s="15">
+        <v>2334702.58</v>
       </c>
       <c r="C21" s="1"/>
     </row>
